--- a/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>BTOG</t>
   </si>
@@ -955,7 +955,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>17500</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1050,8 +1050,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>28600</v>
       </c>
       <c r="E17" s="3">
         <v>5900</v>
@@ -1091,8 +1091,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-24400</v>
       </c>
       <c r="E18" s="3">
         <v>-3800</v>
@@ -1149,8 +1149,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1190,8 +1190,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-21100</v>
       </c>
       <c r="E21" s="3">
         <v>-1500</v>
@@ -1313,8 +1313,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>8</v>
@@ -1395,8 +1395,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-24200</v>
       </c>
       <c r="E26" s="3">
         <v>-4000</v>
@@ -1436,8 +1436,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-24200</v>
       </c>
       <c r="E27" s="3">
         <v>-4000</v>
@@ -1641,8 +1641,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -1682,8 +1682,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-24200</v>
       </c>
       <c r="E33" s="3">
         <v>-4000</v>
@@ -1764,8 +1764,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-24200</v>
       </c>
       <c r="E35" s="3">
         <v>-4000</v>
@@ -2535,7 +2535,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="E58" s="3">
         <v>2700</v>
@@ -2658,7 +2658,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2698,8 +2698,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>8</v>
@@ -3376,8 +3376,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-24200</v>
       </c>
       <c r="E81" s="3">
         <v>-4000</v>
@@ -3862,7 +3862,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4600</v>
+        <v>4000</v>
       </c>
       <c r="E94" s="3">
         <v>300</v>

--- a/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>BTOG</t>
   </si>
@@ -656,202 +656,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E8" s="3">
         <v>4200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>80500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>50000</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>54900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>101100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>77500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>96600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>49900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>91500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43300</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-14300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-34200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-32000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-40500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -867,8 +880,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -908,8 +922,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,40 +966,43 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>17500</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>-800</v>
       </c>
       <c r="H14" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I14" s="3">
         <v>5400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -990,8 +1010,11 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,8 +1054,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,90 +1071,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>28600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>94100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>77200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,35 +1177,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-80600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-24600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1180,54 +1214,60 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1241,99 +1281,105 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1341,16 +1387,19 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1390,90 +1439,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,49 +1571,55 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>3200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-27200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-43400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-8000</v>
-      </c>
-      <c r="J29" s="3">
-        <v>-500</v>
       </c>
       <c r="K29" s="3">
         <v>-500</v>
       </c>
       <c r="L29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M29" s="3">
         <v>4900</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1659,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1636,35 +1703,38 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>80600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>24600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1672,54 +1742,60 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1759,95 +1835,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,8 +1948,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1880,13 +1966,14 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -1895,116 +1982,125 @@
         <v>0</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>7400</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3200</v>
-      </c>
-      <c r="M41" s="3">
-        <v>300</v>
       </c>
       <c r="N41" s="3">
         <v>300</v>
       </c>
       <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1200</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I42" s="3">
-        <v>200</v>
+      <c r="I42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
       </c>
       <c r="K42" s="3">
+        <v>200</v>
+      </c>
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>67000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2017,117 +2113,126 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>800</v>
-      </c>
-      <c r="L44" s="3">
-        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2135,25 +2240,25 @@
         <v>2400</v>
       </c>
       <c r="E47" s="3">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F47" s="3">
         <v>3000</v>
       </c>
       <c r="G47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H47" s="3">
         <v>5700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>600</v>
       </c>
       <c r="J47" s="3">
         <v>600</v>
       </c>
       <c r="K47" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L47" s="3">
         <v>100</v>
@@ -2162,54 +2267,60 @@
         <v>100</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E48" s="3">
         <v>7400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2225,17 +2336,17 @@
       <c r="G49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>5500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>500</v>
       </c>
       <c r="L49" s="3">
         <v>500</v>
@@ -2249,8 +2360,11 @@
       <c r="O49" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2290,8 +2404,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2331,8 +2448,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2342,38 +2462,41 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>18200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2413,49 +2536,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E54" s="3">
         <v>13300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>85900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>51400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2471,8 +2600,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2488,90 +2618,97 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>2100</v>
       </c>
       <c r="I58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J58" s="3">
         <v>12800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2581,88 +2718,94 @@
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>28000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -2673,28 +2816,31 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>2800</v>
       </c>
       <c r="K61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L61" s="3">
         <v>1100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2704,27 +2850,27 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
@@ -2734,8 +2880,11 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2775,8 +2924,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2816,8 +2968,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2857,49 +3012,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>44100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>39500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,8 +3076,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2956,8 +3118,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2997,8 +3162,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3038,8 +3206,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,49 +3250,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-64200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-40000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3161,8 +3338,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3202,8 +3382,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3243,49 +3426,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-12200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3325,95 +3514,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3429,49 +3627,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3511,8 +3713,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3552,8 +3757,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3593,8 +3801,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3634,8 +3845,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3675,49 +3889,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3733,8 +3953,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3760,7 +3981,7 @@
         <v>-700</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3769,13 +3990,16 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3815,8 +4039,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3856,49 +4083,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E94" s="3">
         <v>4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
-      </c>
-      <c r="L94" s="3">
-        <v>1200</v>
       </c>
       <c r="M94" s="3">
         <v>1200</v>
       </c>
       <c r="N94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3914,8 +4147,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3955,8 +4189,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3996,8 +4233,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4037,8 +4277,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4078,54 +4321,60 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -4137,68 +4386,74 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-6900</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7300</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-1400</v>
       </c>
       <c r="I102" s="3">
         <v>-1400</v>
       </c>
       <c r="J102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>BTOG</t>
   </si>
@@ -662,14 +662,11 @@
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -696,22 +693,22 @@
         <v>45291</v>
       </c>
       <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J7" s="2">
         <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44196</v>
       </c>
       <c r="K7" s="2">
         <v>44012</v>
@@ -737,25 +734,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="E8" s="3">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="F8" s="3">
         <v>2100</v>
       </c>
       <c r="G8" s="3">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I8" s="3">
-        <v>80500</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="3">
-        <v>62400</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>24200</v>
@@ -781,25 +778,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3800</v>
+        <v>1900</v>
       </c>
       <c r="E9" s="3">
-        <v>6600</v>
+        <v>1900</v>
       </c>
       <c r="F9" s="3">
-        <v>4200</v>
+        <v>3300</v>
       </c>
       <c r="G9" s="3">
-        <v>400</v>
+        <v>3300</v>
       </c>
       <c r="H9" s="3">
-        <v>14300</v>
+        <v>2100</v>
       </c>
       <c r="I9" s="3">
-        <v>77500</v>
+        <v>2100</v>
       </c>
       <c r="J9" s="3">
-        <v>96600</v>
+        <v>200</v>
       </c>
       <c r="K9" s="3">
         <v>56200</v>
@@ -825,25 +822,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>-900</v>
+        <v>-500</v>
       </c>
       <c r="E10" s="3">
-        <v>-2400</v>
+        <v>-500</v>
       </c>
       <c r="F10" s="3">
-        <v>-2100</v>
+        <v>-1200</v>
       </c>
       <c r="G10" s="3">
-        <v>-200</v>
+        <v>-1200</v>
       </c>
       <c r="H10" s="3">
-        <v>-14300</v>
+        <v>-1100</v>
       </c>
       <c r="I10" s="3">
-        <v>3000</v>
+        <v>-1100</v>
       </c>
       <c r="J10" s="3">
-        <v>-34200</v>
+        <v>-100</v>
       </c>
       <c r="K10" s="3">
         <v>-32000</v>
@@ -974,26 +971,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="G14" s="3">
-        <v>-800</v>
+        <v>8600</v>
       </c>
       <c r="H14" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1019,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,26 +1074,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>4800</v>
       </c>
       <c r="E17" s="3">
-        <v>28600</v>
+        <v>4800</v>
       </c>
       <c r="F17" s="3">
-        <v>5900</v>
+        <v>5700</v>
       </c>
       <c r="G17" s="3">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="H17" s="3">
-        <v>900</v>
+        <v>3000</v>
       </c>
       <c r="I17" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="J17" s="3">
-        <v>63200</v>
+        <v>2300</v>
       </c>
       <c r="K17" s="3">
         <v>3400</v>
@@ -1121,26 +1118,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-3400</v>
       </c>
       <c r="E18" s="3">
-        <v>-24400</v>
+        <v>-3400</v>
       </c>
       <c r="F18" s="3">
-        <v>-3800</v>
+        <v>-3600</v>
       </c>
       <c r="G18" s="3">
-        <v>-5300</v>
+        <v>-3600</v>
       </c>
       <c r="H18" s="3">
-        <v>-900</v>
+        <v>-1900</v>
       </c>
       <c r="I18" s="3">
-        <v>77200</v>
+        <v>-1900</v>
       </c>
       <c r="J18" s="3">
-        <v>-800</v>
+        <v>-2200</v>
       </c>
       <c r="K18" s="3">
         <v>20800</v>
@@ -1183,26 +1180,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-80600</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-24600</v>
@@ -1227,26 +1224,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-3100</v>
       </c>
       <c r="E21" s="3">
-        <v>-21100</v>
+        <v>-3100</v>
       </c>
       <c r="F21" s="3">
-        <v>-1500</v>
+        <v>-1900</v>
       </c>
       <c r="G21" s="3">
-        <v>-5000</v>
+        <v>-1900</v>
       </c>
       <c r="H21" s="3">
-        <v>-900</v>
+        <v>-700</v>
       </c>
       <c r="I21" s="3">
-        <v>-3500</v>
+        <v>-700</v>
       </c>
       <c r="J21" s="3">
-        <v>-600</v>
+        <v>-2100</v>
       </c>
       <c r="K21" s="3">
         <v>-3300</v>
@@ -1284,13 +1281,13 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1316,25 +1313,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7100</v>
+        <v>-3500</v>
       </c>
       <c r="E23" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F23" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G23" s="3">
-        <v>-5300</v>
+        <v>-12100</v>
       </c>
       <c r="H23" s="3">
-        <v>-900</v>
+        <v>-2000</v>
       </c>
       <c r="I23" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="J23" s="3">
-        <v>-1100</v>
+        <v>-2200</v>
       </c>
       <c r="K23" s="3">
         <v>-3900</v>
@@ -1362,23 +1359,23 @@
       <c r="D24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1447,26 +1444,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-3500</v>
       </c>
       <c r="E26" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F26" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G26" s="3">
-        <v>-5300</v>
+        <v>-12100</v>
       </c>
       <c r="H26" s="3">
-        <v>-900</v>
+        <v>-2000</v>
       </c>
       <c r="I26" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="J26" s="3">
-        <v>-1200</v>
+        <v>-2200</v>
       </c>
       <c r="K26" s="3">
         <v>-3900</v>
@@ -1491,26 +1488,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-3500</v>
       </c>
       <c r="E27" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F27" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>-12100</v>
       </c>
       <c r="H27" s="3">
-        <v>3500</v>
+        <v>-2000</v>
       </c>
       <c r="I27" s="3">
-        <v>-2200</v>
+        <v>-2000</v>
       </c>
       <c r="J27" s="3">
-        <v>-1600</v>
+        <v>13500</v>
       </c>
       <c r="K27" s="3">
         <v>-4400</v>
@@ -1579,8 +1576,8 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1589,16 +1586,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-27200</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-43400</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-8000</v>
+        <v>15200</v>
       </c>
       <c r="K29" s="3">
         <v>-500</v>
@@ -1711,26 +1708,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>80600</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>24600</v>
@@ -1755,26 +1752,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-3500</v>
       </c>
       <c r="E33" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F33" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G33" s="3">
-        <v>3200</v>
+        <v>-12100</v>
       </c>
       <c r="H33" s="3">
-        <v>-23800</v>
+        <v>-2000</v>
       </c>
       <c r="I33" s="3">
-        <v>-45600</v>
+        <v>-2000</v>
       </c>
       <c r="J33" s="3">
-        <v>-9600</v>
+        <v>13500</v>
       </c>
       <c r="K33" s="3">
         <v>-4900</v>
@@ -1843,26 +1840,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-3500</v>
       </c>
       <c r="E35" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F35" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G35" s="3">
-        <v>3200</v>
+        <v>-12100</v>
       </c>
       <c r="H35" s="3">
-        <v>-23800</v>
+        <v>-2000</v>
       </c>
       <c r="I35" s="3">
-        <v>-45600</v>
+        <v>-2000</v>
       </c>
       <c r="J35" s="3">
-        <v>-9600</v>
+        <v>13500</v>
       </c>
       <c r="K35" s="3">
         <v>-4900</v>
@@ -1896,22 +1893,22 @@
         <v>45291</v>
       </c>
       <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J38" s="2">
         <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44196</v>
       </c>
       <c r="K38" s="2">
         <v>44012</v>
@@ -1976,7 +1973,7 @@
         <v>6900</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -1985,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>7400</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K41" s="3">
         <v>1500</v>
@@ -2017,25 +2014,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
@@ -2064,22 +2061,22 @@
         <v>1500</v>
       </c>
       <c r="E43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3">
         <v>2900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J43" s="3">
         <v>4400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>30000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>67000</v>
       </c>
       <c r="K43" s="3">
         <v>40700</v>
@@ -2116,14 +2113,14 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
@@ -2149,25 +2146,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>2400</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>2200</v>
+        <v>2700</v>
       </c>
       <c r="G45" s="3">
-        <v>200</v>
+        <v>2700</v>
       </c>
       <c r="H45" s="3">
-        <v>200</v>
+        <v>3100</v>
       </c>
       <c r="I45" s="3">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="J45" s="3">
-        <v>5700</v>
+        <v>1300</v>
       </c>
       <c r="K45" s="3">
         <v>7800</v>
@@ -2196,22 +2193,22 @@
         <v>9100</v>
       </c>
       <c r="E46" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F46" s="3">
         <v>3600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H46" s="3">
         <v>6500</v>
       </c>
-      <c r="G46" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>14200</v>
-      </c>
       <c r="I46" s="3">
-        <v>32500</v>
+        <v>6500</v>
       </c>
       <c r="J46" s="3">
-        <v>73200</v>
+        <v>23900</v>
       </c>
       <c r="K46" s="3">
         <v>50300</v>
@@ -2243,19 +2240,19 @@
         <v>2400</v>
       </c>
       <c r="F47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H47" s="3">
         <v>3000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="H47" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>6000</v>
-      </c>
       <c r="J47" s="3">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="K47" s="3">
         <v>600</v>
@@ -2284,22 +2281,22 @@
         <v>1900</v>
       </c>
       <c r="E48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H48" s="3">
         <v>27000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J48" s="3">
         <v>8000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>9200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>5400</v>
       </c>
       <c r="K48" s="3">
         <v>6200</v>
@@ -2324,26 +2321,26 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>5600</v>
@@ -2465,17 +2462,17 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>18200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>1200</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>600</v>
@@ -2548,22 +2545,22 @@
         <v>13500</v>
       </c>
       <c r="E54" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F54" s="3">
         <v>13300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>13300</v>
+      </c>
+      <c r="H54" s="3">
         <v>36600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>36600</v>
+      </c>
+      <c r="J54" s="3">
         <v>35000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>29300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>40900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>85900</v>
       </c>
       <c r="K54" s="3">
         <v>63300</v>
@@ -2624,26 +2621,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1000</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F57" s="3">
+        <v>700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>700</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
-        <v>300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>10700</v>
-      </c>
       <c r="I57" s="3">
-        <v>10200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>16100</v>
+        <v>100</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>9500</v>
@@ -2669,25 +2666,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2100</v>
-      </c>
       <c r="I58" s="3">
-        <v>2100</v>
+        <v>2700</v>
       </c>
       <c r="J58" s="3">
-        <v>12800</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>14900</v>
@@ -2712,26 +2709,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>300</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>28000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>26400</v>
+        <v>300</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J59" s="3">
-        <v>21000</v>
+        <v>300</v>
       </c>
       <c r="K59" s="3">
         <v>8400</v>
@@ -2760,22 +2757,22 @@
         <v>1600</v>
       </c>
       <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>40800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>38700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>49900</v>
       </c>
       <c r="K60" s="3">
         <v>32700</v>
@@ -2801,16 +2798,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1400</v>
+        <v>2900</v>
       </c>
       <c r="E61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2819,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>2800</v>
@@ -2853,17 +2850,17 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1100</v>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>1000</v>
@@ -3024,22 +3021,22 @@
         <v>4500</v>
       </c>
       <c r="E66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J66" s="3">
         <v>300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>41500</v>
-      </c>
-      <c r="I66" s="3">
-        <v>44100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>57200</v>
       </c>
       <c r="K66" s="3">
         <v>39500</v>
@@ -3262,22 +3259,22 @@
         <v>-71300</v>
       </c>
       <c r="E72" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-64200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-64200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-40000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-36000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-60700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-36900</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-900</v>
       </c>
       <c r="K72" s="3">
         <v>8700</v>
@@ -3438,22 +3435,22 @@
         <v>9000</v>
       </c>
       <c r="E76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F76" s="3">
         <v>10300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H76" s="3">
         <v>33800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J76" s="3">
         <v>34700</v>
-      </c>
-      <c r="H76" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>28700</v>
       </c>
       <c r="K76" s="3">
         <v>23800</v>
@@ -3531,22 +3528,22 @@
         <v>45291</v>
       </c>
       <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="J80" s="2">
         <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44377</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44196</v>
       </c>
       <c r="K80" s="2">
         <v>44012</v>
@@ -3571,26 +3568,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-3500</v>
       </c>
       <c r="E81" s="3">
-        <v>-24200</v>
+        <v>-3500</v>
       </c>
       <c r="F81" s="3">
-        <v>-4000</v>
+        <v>-12100</v>
       </c>
       <c r="G81" s="3">
-        <v>3200</v>
+        <v>-12100</v>
       </c>
       <c r="H81" s="3">
-        <v>-23800</v>
+        <v>-2000</v>
       </c>
       <c r="I81" s="3">
-        <v>-45600</v>
+        <v>-2000</v>
       </c>
       <c r="J81" s="3">
-        <v>-9600</v>
+        <v>13500</v>
       </c>
       <c r="K81" s="3">
         <v>-4900</v>
@@ -3634,25 +3631,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="F83" s="3">
-        <v>2400</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -3898,25 +3895,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4600</v>
+        <v>-2300</v>
       </c>
       <c r="E89" s="3">
-        <v>-3600</v>
+        <v>-2300</v>
       </c>
       <c r="F89" s="3">
-        <v>-3200</v>
+        <v>-1800</v>
       </c>
       <c r="G89" s="3">
-        <v>-14300</v>
+        <v>-1800</v>
       </c>
       <c r="H89" s="3">
-        <v>100</v>
+        <v>-1600</v>
       </c>
       <c r="I89" s="3">
-        <v>-10500</v>
+        <v>-1600</v>
       </c>
       <c r="J89" s="3">
-        <v>-11100</v>
+        <v>-7200</v>
       </c>
       <c r="K89" s="3">
         <v>-5900</v>
@@ -3959,23 +3956,23 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1300</v>
-      </c>
       <c r="G91" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J91" s="3">
         <v>-700</v>
@@ -4092,25 +4089,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>3700</v>
+        <v>1900</v>
       </c>
       <c r="E94" s="3">
-        <v>4000</v>
+        <v>1900</v>
       </c>
       <c r="F94" s="3">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G94" s="3">
-        <v>-11300</v>
+        <v>2000</v>
       </c>
       <c r="H94" s="3">
-        <v>-7000</v>
+        <v>100</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="K94" s="3">
         <v>200</v>
@@ -4153,26 +4150,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4330,25 +4327,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7800</v>
+        <v>3900</v>
       </c>
       <c r="E100" s="3">
-        <v>-400</v>
+        <v>3900</v>
       </c>
       <c r="F100" s="3">
-        <v>2900</v>
+        <v>-200</v>
       </c>
       <c r="G100" s="3">
-        <v>26000</v>
+        <v>-200</v>
       </c>
       <c r="H100" s="3">
-        <v>14200</v>
+        <v>1400</v>
       </c>
       <c r="I100" s="3">
-        <v>8700</v>
+        <v>1400</v>
       </c>
       <c r="J100" s="3">
-        <v>9500</v>
+        <v>5900</v>
       </c>
       <c r="K100" s="3">
         <v>4100</v>
@@ -4376,8 +4373,8 @@
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -4389,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4418,25 +4415,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6900</v>
+        <v>3400</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>7300</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>-1400</v>
+        <v>-3400</v>
       </c>
       <c r="K102" s="3">
         <v>-1700</v>

--- a/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>BTOG</t>
   </si>
@@ -656,212 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>1400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>24200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>50000</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>54900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>101100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>1900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>56200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>46100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>40500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>49900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>91500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>43300</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>-500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-32000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-40500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>9600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +904,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +950,14 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,29 +1000,35 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>8600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>8600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1001,47 +1041,53 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>1500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,8 +1100,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1121,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>49500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>52700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>94100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>20800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,104 +1241,118 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-24600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1287,72 +1367,84 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
         <v>500</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-12100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,26 +1469,32 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1537,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-12100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-12100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-12100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-12100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1687,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1595,28 +1717,34 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>15200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>4900</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1787,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1837,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>24600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-12100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-12100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1987,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-12100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-12100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2116,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,23 +2136,25 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>6900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
@@ -1991,25 +2165,31 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2035,69 +2215,81 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>40700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>44400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>39800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>39100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>26900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2125,119 +2317,137 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
-      </c>
-      <c r="N44" s="3">
-        <v>100</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F46" s="3">
         <v>9100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>9100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>50300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>50900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>41100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>29000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2400</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>2400</v>
@@ -2246,78 +2456,90 @@
         <v>2400</v>
       </c>
       <c r="H47" s="3">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="I47" s="3">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="J47" s="3">
         <v>3000</v>
       </c>
       <c r="K47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M47" s="3">
         <v>600</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>100</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>1900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>27000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2343,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>5600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>500</v>
-      </c>
-      <c r="M49" s="3">
-        <v>500</v>
       </c>
       <c r="N49" s="3">
         <v>500</v>
@@ -2360,8 +2582,14 @@
       <c r="P49" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>500</v>
+      </c>
+      <c r="R49" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2632,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2682,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2474,26 +2714,32 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2782,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F54" s="3">
         <v>13500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>36600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>35000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>63300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>51400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>47600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>33700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2856,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,8 +2876,10 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2627,217 +2889,247 @@
       <c r="E57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>9500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>14900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>13800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>9800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>9400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>600</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>8400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>32700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>30000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>22800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>29300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>16900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2862,26 +3154,32 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3222,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3272,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3322,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>39500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>32200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>26800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>30300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>17900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3396,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3442,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3492,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3542,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3592,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-71300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-71300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-64200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-64200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-40000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-40000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-36000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>8700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>13000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>13600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3692,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3742,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3792,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F76" s="3">
         <v>9000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>33800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>33800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>34700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>23800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>24600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>24500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>17400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>15800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3892,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-12100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-12100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4021,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4117,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4167,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4217,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4267,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4317,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4391,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3962,41 +4404,47 @@
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4487,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4537,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4611,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,11 +4639,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4189,8 +4657,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4707,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4757,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4807,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>5900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4376,11 +4874,11 @@
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -4389,43 +4887,49 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F102" s="3">
         <v>3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -4433,24 +4937,30 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2900</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTOG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>BTOG</t>
   </si>
@@ -656,238 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>1400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>24200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>50000</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>54900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>101100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>56200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>46100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>40500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>49900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>91500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>43300</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>-500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-1200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-32000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-40500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>9600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +931,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +983,14 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,35 +1039,41 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>4500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>8600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>8600</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1047,53 +1086,59 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1174,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>-400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>-400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>49500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>52700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>94100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>20800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,58 +1308,66 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-24600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1305,46 +1378,52 @@
         <v>-1000</v>
       </c>
       <c r="F21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>6300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1355,10 +1434,10 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1373,78 +1452,90 @@
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-12100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1475,26 +1566,32 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-12100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-12100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>13500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1723,28 +1844,34 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>15200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>4900</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1976,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>24600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-12100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>13500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-12100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>13500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,29 +2309,31 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6900</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
@@ -2171,25 +2344,31 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2221,75 +2400,87 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F43" s="3">
         <v>5100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>40700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>44400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>39800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>39100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>26900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2323,23 +2514,29 @@
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>100</v>
-      </c>
-      <c r="P44" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2350,96 +2547,108 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F46" s="3">
         <v>6700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>50300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>50900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>45700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>41100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>29000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2449,11 +2658,11 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2400</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
         <v>2400</v>
@@ -2462,34 +2671,40 @@
         <v>2400</v>
       </c>
       <c r="J47" s="3">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="K47" s="3">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="L47" s="3">
         <v>3000</v>
       </c>
       <c r="M47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O47" s="3">
         <v>600</v>
-      </c>
-      <c r="N47" s="3">
-        <v>100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>100</v>
       </c>
       <c r="P47" s="3">
         <v>100</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2499,47 +2714,53 @@
       <c r="E48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>27000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2571,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>5600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>500</v>
+      </c>
+      <c r="T49" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2921,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2720,26 +2959,32 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +3033,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F54" s="3">
         <v>6700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>36600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>35000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>63300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>56900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>51400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>47600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>33700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,8 +3137,10 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2895,241 +3156,271 @@
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>9500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>9900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>14900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>13800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>9800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>9400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>8400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>32700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>30000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>22800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>29300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>16900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3160,26 +3451,32 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3637,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F66" s="3">
         <v>5800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>39500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>26800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>30300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>17900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3883,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-81700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-81700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-71300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-71300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-64200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-64200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-40000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-40000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-36000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>8700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>13000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>13600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +4163,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>33800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>33800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>34700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>23800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>24600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>24500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-12100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>13500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,58 +4418,66 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>500</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4750,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4832,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4410,41 +4851,47 @@
       <c r="G91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4996,70 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4645,11 +5112,11 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5298,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>5900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>6700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4880,11 +5377,11 @@
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -4893,49 +5390,55 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3400</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -4943,24 +5446,30 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1500</v>
       </c>
     </row>
